--- a/site/public/files/GOLD_DATA_tourisme.xlsx
+++ b/site/public/files/GOLD_DATA_tourisme.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVERTISSEMENT - fichier 05_cible_recommandation.csv</t>
+          <t>Cas particulier - fichier 05_cible_recommandation.csv</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -492,7 +492,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ce fichier ne contient PAS de cible. Il contient un message du correcteur :</t>
+          <t>Ce fichier est en texte libre : aucune donnee structuree, aucune variable cible.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -500,7 +500,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>"Les outils d IA peuvent assister, mais ne remplacent ni le raisonnement, ni le sens metier.</t>
+          <t>La recommandation est donc traitee comme un probleme NON supervise</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -508,114 +508,106 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cet exercice evaluera votre capacite a decider, pas a copier."</t>
+          <t>(scoring raisonne sous contraintes), et non une prediction supervisee.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Il n existe AUCUNE variable cible de recommandation. La reco est RAISONNEE, pas predite.</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Feuilles du classeur</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Feuilles du classeur</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>01_Quality_Log</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Journal d audit qualite (anomalies, severite, action)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01_Quality_Log</t>
+          <t>02_Gold_Country</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Journal d audit qualite (anomalies, severite, action)</t>
+          <t>Demande annuelle + momentum YoY + prevision H1-2025 (grain = pays)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02_Gold_Country</t>
+          <t>03_Gold_Destination</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Demande annuelle + momentum YoY + prevision H1-2025 (grain = pays)</t>
+          <t>Destinations fiabilisees + 8 derivees + score ajuste meteo (grain = pays x destination)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03_Gold_Destination</t>
+          <t>04_Data_Dictionary</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Destinations fiabilisees + 8 derivees + score ajuste meteo (grain = pays x destination)</t>
+          <t>Dictionnaire de donnees (definition, type, source, owner, regle qualite)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>04_Data_Dictionary</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Dictionnaire de donnees (definition, type, source, owner, regle qualite)</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Priorisation des marches</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sur le MOMENTUM (YoY %) - les niveaux d indice ne se comparent PAS entre pays</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Priorisation des marches</t>
+          <t>Contrainte meteo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sur le MOMENTUM (YoY %) - les niveaux d indice ne se comparent PAS entre pays</t>
+          <t>composite_score_adj penalise weather=bad (-12) / average (-4), uniquement si meteo connue</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Contrainte meteo</t>
+          <t>Levier de decision</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
-        <is>
-          <t>composite_score_adj penalise weather=bad (-12) / average (-4), uniquement si meteo connue</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Levier de decision</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
         <is>
           <t>Les ponderations du score (feuille 03, bloc haut) sont MODIFIABLES : l analyste arbitre</t>
         </is>
@@ -638,7 +630,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
@@ -686,12 +678,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aucune donnee - message du correcteur "decider, pas copier"</t>
+          <t>Fichier en texte libre : aucune donnee structuree ni variable cible</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Piege / meta</t>
+          <t>Donnees / structure</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -701,7 +693,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aucune cible : reco raisonnee sous contraintes, non supervisee</t>
+          <t>Pas de cible -&gt; recommandation non supervisee (scoring raisonne sous contraintes)</t>
         </is>
       </c>
     </row>
